--- a/data/trans_orig/P79_n_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R-Habitat-trans_orig.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>803</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>700</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>24129</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>36258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>14963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28124</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37985</t>
+          <t>45761</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>33833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51624</t>
+          <t>61409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -1167,32 +1167,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29833</t>
+          <t>35364</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39875</t>
+          <t>49363</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1202,32 +1202,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>51784</t>
+          <t>60062</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39264</t>
+          <t>48190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65234</t>
+          <t>73857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1237,32 +1237,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>81617</t>
+          <t>95426</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66563</t>
+          <t>79935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98143</t>
+          <t>114884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -1278,32 +1278,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>584556</t>
+          <t>629225</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>570619</t>
+          <t>612068</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>597733</t>
+          <t>644018</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1313,32 +1313,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>653950</t>
+          <t>651786</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>638179</t>
+          <t>635944</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>669544</t>
+          <t>667431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1348,32 +1348,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1238506</t>
+          <t>1281011</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1215151</t>
+          <t>1259443</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1257576</t>
+          <t>1301551</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -1391,17 +1391,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>676</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>676</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -1652,22 +1652,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1687,32 +1687,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -1728,102 +1728,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4671</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1724</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9502</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>11289</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>5825</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>23901</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3233</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7458</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>9520</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>3882</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>21382</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1839,32 +1839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>29742</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>24519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1874,32 +1874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34422</t>
+          <t>39948</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46958</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1909,32 +1909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>64164</t>
+          <t>74586</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40898</t>
+          <t>58702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82789</t>
+          <t>92398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1950,32 +1950,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81463</t>
+          <t>93187</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>74274</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>115224</t>
+          <t>116008</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1985,32 +1985,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84668</t>
+          <t>97047</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71275</t>
+          <t>81595</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100946</t>
+          <t>116380</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2020,32 +2020,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>166131</t>
+          <t>190235</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>109109</t>
+          <t>164600</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>199886</t>
+          <t>218793</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -2061,32 +2061,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1075372</t>
+          <t>914473</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1033429</t>
+          <t>888932</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1139254</t>
+          <t>937759</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2096,32 +2096,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>832174</t>
+          <t>925628</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>814598</t>
+          <t>903069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>849234</t>
+          <t>943737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2131,32 +2131,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1907547</t>
+          <t>1840101</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1862652</t>
+          <t>1806094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1990789</t>
+          <t>1869761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>88,18%</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>762</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>762</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2546,32 +2546,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26911</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2581,32 +2581,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>23687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2622,67 +2622,67 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22523</t>
+          <t>24186</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38865</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>25317</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>16256</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>36614</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>20278</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>8692</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>31789</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2692,32 +2692,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42802</t>
+          <t>49503</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>37636</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>62078</t>
+          <t>67633</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>59730</t>
+          <t>72096</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45206</t>
+          <t>54727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78604</t>
+          <t>94297</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2768,32 +2768,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>44323</t>
+          <t>56637</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20609</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63144</t>
+          <t>71606</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2803,32 +2803,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>104053</t>
+          <t>128733</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68836</t>
+          <t>106501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131444</t>
+          <t>155706</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -2844,32 +2844,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>616835</t>
+          <t>701208</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592919</t>
+          <t>675226</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>636305</t>
+          <t>722727</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2879,32 +2879,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>860868</t>
+          <t>723849</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>832415</t>
+          <t>704848</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>900440</t>
+          <t>740074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2914,32 +2914,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1477702</t>
+          <t>1425058</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1438534</t>
+          <t>1393643</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1530410</t>
+          <t>1450570</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -2957,17 +2957,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3027,17 +3027,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>705</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -3183,32 +3183,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>675</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3253,32 +3253,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -3294,32 +3294,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12579</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3329,32 +3329,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3364,32 +3364,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>17754</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3405,32 +3405,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>40200</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44830</t>
+          <t>55863</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3440,32 +3440,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25701</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48389</t>
+          <t>56784</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3475,32 +3475,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>68700</t>
+          <t>83111</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>52617</t>
+          <t>66959</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84792</t>
+          <t>101111</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3516,32 +3516,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>113109</t>
+          <t>133857</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>92945</t>
+          <t>111048</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>136327</t>
+          <t>157643</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3551,32 +3551,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>135691</t>
+          <t>153896</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>109279</t>
+          <t>134965</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>159713</t>
+          <t>176098</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3586,32 +3586,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>248801</t>
+          <t>287753</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>215408</t>
+          <t>258274</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>280567</t>
+          <t>320141</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -3627,32 +3627,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>772823</t>
+          <t>806667</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>743859</t>
+          <t>775839</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>795281</t>
+          <t>831785</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3662,32 +3662,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>918477</t>
+          <t>916855</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>891568</t>
+          <t>891389</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>951544</t>
+          <t>938108</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3697,32 +3697,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1691300</t>
+          <t>1723523</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1656213</t>
+          <t>1687206</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1735298</t>
+          <t>1755811</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -3740,17 +3740,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
     </row>
@@ -3966,22 +3966,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4077,32 +4077,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>33056</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4112,32 +4112,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>33079</t>
+          <t>27247</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4147,32 +4147,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>32678</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20953</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>53224</t>
+          <t>50832</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -4188,32 +4188,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>103920</t>
+          <t>123153</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>78830</t>
+          <t>101307</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>129856</t>
+          <t>150312</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4223,32 +4223,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>129808</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>85867</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>132514</t>
+          <t>153597</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4258,32 +4258,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>213650</t>
+          <t>252961</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>178767</t>
+          <t>220220</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>248984</t>
+          <t>285372</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -4299,32 +4299,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>284135</t>
+          <t>334505</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>227212</t>
+          <t>296308</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>328963</t>
+          <t>371703</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4334,32 +4334,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>316467</t>
+          <t>367642</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>258908</t>
+          <t>334313</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>353173</t>
+          <t>401881</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4369,32 +4369,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>600602</t>
+          <t>702147</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>516364</t>
+          <t>646586</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>661283</t>
+          <t>752580</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -4410,32 +4410,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3049587</t>
+          <t>3051574</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2992170</t>
+          <t>3000343</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3137027</t>
+          <t>3096532</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4445,32 +4445,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3265469</t>
+          <t>3218118</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3217920</t>
+          <t>3176703</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3349284</t>
+          <t>3255797</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4480,32 +4480,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>6315056</t>
+          <t>6269692</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6237420</t>
+          <t>6207759</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6439604</t>
+          <t>6331232</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -4523,17 +4523,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4593,17 +4593,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
